--- a/tools/importer/reports/import-event-page.report.xlsx
+++ b/tools/importer/reports/import-event-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="185">
   <si>
     <t>_reportFile</t>
   </si>
@@ -43,28 +43,43 @@
     <t>url</t>
   </si>
   <si>
+    <t>innovation-theater.report.json</t>
+  </si>
+  <si>
+    <t>["event-hero","video-text","theater-sessions"]</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>innovation-theater</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>2026-08-21T10:19:55.237Z</t>
+  </si>
+  <si>
+    <t>GE HealthCare Events Center</t>
+  </si>
+  <si>
+    <t>https://events.gehealthcare.com/innovation-theater/</t>
+  </si>
+  <si>
     <t>news.report.json</t>
   </si>
   <si>
     <t>[]</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>news</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>news-article</t>
   </si>
   <si>
-    <t>2026-08-21T06:51:52.996Z</t>
-  </si>
-  <si>
-    <t>GE HealthCare Events Center</t>
+    <t>2026-08-21T07:14:56.863Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/news/</t>
@@ -79,7 +94,7 @@
     <t>event-stub</t>
   </si>
   <si>
-    <t>2026-08-21T06:47:42.281Z</t>
+    <t>2026-08-21T07:13:22.466Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/aami-exchange/</t>
@@ -97,7 +112,7 @@
     <t>event-page</t>
   </si>
   <si>
-    <t>2026-08-21T07:08:38.051Z</t>
+    <t>2026-08-21T10:22:40.025Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/acc-2024/</t>
@@ -109,7 +124,7 @@
     <t>events/acc-2026</t>
   </si>
   <si>
-    <t>2026-08-21T07:11:11.575Z</t>
+    <t>2026-08-21T10:26:41.162Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/acc-2026/</t>
@@ -121,7 +136,7 @@
     <t>events/arab-health-2025</t>
   </si>
   <si>
-    <t>2026-08-21T06:46:43.312Z</t>
+    <t>2026-08-21T07:12:35.327Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/arab-health-2025/</t>
@@ -136,7 +151,7 @@
     <t>events/asci-2025</t>
   </si>
   <si>
-    <t>2026-08-21T07:09:57.862Z</t>
+    <t>2026-08-21T10:24:36.572Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/asci-2025/</t>
@@ -151,7 +166,7 @@
     <t>events/asnc-2025</t>
   </si>
   <si>
-    <t>2026-08-21T07:10:17.900Z</t>
+    <t>2026-08-21T10:25:04.553Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/asnc-2025/</t>
@@ -163,7 +178,7 @@
     <t>events/astro-2024</t>
   </si>
   <si>
-    <t>2026-08-21T07:09:47.688Z</t>
+    <t>2026-08-21T10:24:19.372Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/astro-2024/</t>
@@ -175,7 +190,7 @@
     <t>events/astro-2025</t>
   </si>
   <si>
-    <t>2026-08-21T07:10:07.171Z</t>
+    <t>2026-08-21T10:24:54.954Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/astro-2025/</t>
@@ -190,7 +205,7 @@
     <t>events/eanm-2025</t>
   </si>
   <si>
-    <t>2026-08-21T07:10:26.391Z</t>
+    <t>2026-08-21T10:25:21.339Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/eanm-2025/</t>
@@ -205,7 +220,7 @@
     <t>events/ecr-2026-2</t>
   </si>
   <si>
-    <t>2026-08-21T07:11:03.374Z</t>
+    <t>2026-08-21T10:26:22.524Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/ecr-2026-2/</t>
@@ -217,7 +232,7 @@
     <t>events/effortless-2023</t>
   </si>
   <si>
-    <t>2026-08-21T07:10:43.075Z</t>
+    <t>2026-08-21T10:25:55.354Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/effortless-2023/</t>
@@ -229,7 +244,7 @@
     <t>events/esc-2024</t>
   </si>
   <si>
-    <t>2026-08-21T07:08:49.854Z</t>
+    <t>2026-08-21T10:22:57.131Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/esc-2024/</t>
@@ -241,7 +256,7 @@
     <t>events/esc-2026</t>
   </si>
   <si>
-    <t>2026-08-21T07:12:14.155Z</t>
+    <t>2026-08-21T10:28:49.590Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/esc-2026/</t>
@@ -256,7 +271,7 @@
     <t>events/estro-2026</t>
   </si>
   <si>
-    <t>2026-08-21T07:11:39.787Z</t>
+    <t>2026-08-21T10:27:29.907Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/estro-2026/</t>
@@ -268,7 +283,7 @@
     <t>events/excon-2024</t>
   </si>
   <si>
-    <t>2026-08-21T06:46:12.602Z</t>
+    <t>2026-08-21T07:12:20.586Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/excon-2024/</t>
@@ -280,7 +295,7 @@
     <t>events/excon-2025</t>
   </si>
   <si>
-    <t>2026-08-21T06:46:26.977Z</t>
+    <t>2026-08-21T07:12:28.713Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/excon-2025/</t>
@@ -292,7 +307,7 @@
     <t>events/ge-healthcare-webinar-vizamyl-flutemetamol-f-18-injection-expanded-indications-for-positron-emission-tomography-imaging-and-quantification-overview</t>
   </si>
   <si>
-    <t>2026-08-21T06:46:57.780Z</t>
+    <t>2026-08-21T07:12:44.225Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/ge-healthcare-webinar-vizamyl-flutemetamol-f-18-injection-expanded-indications-for-positron-emission-tomography-imaging-and-quantification-overview/</t>
@@ -304,7 +319,7 @@
     <t>events/gest-2024</t>
   </si>
   <si>
-    <t>2026-08-21T07:10:33.420Z</t>
+    <t>2026-08-21T10:25:39.673Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/gest-2024/</t>
@@ -316,7 +331,7 @@
     <t>events/himss-2026</t>
   </si>
   <si>
-    <t>2026-08-21T07:11:51.828Z</t>
+    <t>2026-08-21T10:28:23.596Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/himss-2026/</t>
@@ -328,7 +343,7 @@
     <t>events/ismrm-2026</t>
   </si>
   <si>
-    <t>2026-08-21T07:11:29.682Z</t>
+    <t>2026-08-21T10:27:12.693Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/ismrm-2026/</t>
@@ -340,7 +355,7 @@
     <t>events/rsna-2025-2</t>
   </si>
   <si>
-    <t>2026-08-21T07:10:53.984Z</t>
+    <t>2026-08-21T10:26:11.504Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/rsna-2025-2/</t>
@@ -355,7 +370,7 @@
     <t>events/rsna-2026</t>
   </si>
   <si>
-    <t>2026-08-21T07:08:25.855Z</t>
+    <t>2026-08-21T10:22:20.256Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/rsna-2026/</t>
@@ -367,7 +382,7 @@
     <t>events/scct-2023</t>
   </si>
   <si>
-    <t>2026-08-21T07:09:38.370Z</t>
+    <t>2026-08-21T10:24:00.405Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/scct-2023/</t>
@@ -379,7 +394,7 @@
     <t>events/scct-2025</t>
   </si>
   <si>
-    <t>2026-08-21T07:12:01.657Z</t>
+    <t>2026-08-21T10:28:41.531Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/scct-2025/</t>
@@ -391,7 +406,7 @@
     <t>events/snmmi-2024</t>
   </si>
   <si>
-    <t>2026-08-21T07:08:58.819Z</t>
+    <t>2026-08-21T10:23:14.431Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/snmmi-2024/</t>
@@ -403,7 +418,7 @@
     <t>events/snmmi-2026</t>
   </si>
   <si>
-    <t>2026-08-21T07:11:20.158Z</t>
+    <t>2026-08-21T10:26:57.208Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/events/snmmi-2026/</t>
@@ -415,7 +430,7 @@
     <t>news/ge-healthcare-and-starvision-collaborate-to-scale-remote-scanning-in-germany-using-imaging-360-remote-powered-by-ncommand-lite</t>
   </si>
   <si>
-    <t>2026-08-21T06:51:28.811Z</t>
+    <t>2026-08-21T07:14:34.008Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/news/ge-healthcare-and-starvision-collaborate-to-scale-remote-scanning-in-germany-using-imaging-360-remote-powered-by-ncommand-lite/</t>
@@ -427,7 +442,7 @@
     <t>news/ge-healthcare-announces-flyrcado-milestone-strong-pilot-results-drive-broader-rollout-at-cvausa</t>
   </si>
   <si>
-    <t>2026-08-21T06:50:50.260Z</t>
+    <t>2026-08-21T07:13:56.672Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/news/ge-healthcare-announces-flyrcado-milestone-strong-pilot-results-drive-broader-rollout-at-cvausa/</t>
@@ -439,7 +454,7 @@
     <t>news/ge-healthcare-introduces-genesis-radiology-workspace-a-cloud-first-solution-with-a-goal-for-smarter-faster-diagnosis</t>
   </si>
   <si>
-    <t>2026-08-21T06:50:40.641Z</t>
+    <t>2026-08-21T07:13:48.415Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/news/ge-healthcare-introduces-genesis-radiology-workspace-a-cloud-first-solution-with-a-goal-for-smarter-faster-diagnosis/</t>
@@ -451,7 +466,7 @@
     <t>news/ge-healthcare-to-acquire-intelerad-advancing-cloud-enabled-enterprise-imaging-across-care-settings</t>
   </si>
   <si>
-    <t>2026-08-21T06:51:37.796Z</t>
+    <t>2026-08-21T07:14:43.243Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/news/ge-healthcare-to-acquire-intelerad-advancing-cloud-enabled-enterprise-imaging-across-care-settings/</t>
@@ -463,7 +478,7 @@
     <t>news/ge-healthcare-unveils-pristina-recon-dl-for-mammography-deep-learning-image-reconstruction-technology-delivering-clearer-image-quality</t>
   </si>
   <si>
-    <t>2026-08-21T06:50:29.540Z</t>
+    <t>2026-08-21T07:13:37.979Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/news/ge-healthcare-unveils-pristina-recon-dl-for-mammography-deep-learning-image-reconstruction-technology-delivering-clearer-image-quality/</t>
@@ -475,7 +490,7 @@
     <t>news/ge-healthcares-photonova-spectra-with-deep-silicon-reimagines-photon-counting-ct-to-see-more-know-more-and-achieve-more</t>
   </si>
   <si>
-    <t>2026-08-21T06:50:18.895Z</t>
+    <t>2026-08-21T07:13:29.956Z</t>
   </si>
   <si>
     <t>https://events.gehealthcare.com/news/ge-healthcares-photonova-spectra-with-deep-silicon-reimagines-photon-counting-ct-to-see-more-know-more-and-achieve-more/</t>
@@ -941,11 +956,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="5" width="50" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="26" customWidth="1"/>
     <col min="9" max="9" width="29" customWidth="1"/>
     <col min="10" max="10" width="50" customWidth="1"/>
@@ -1003,24 +1018,24 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
       <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
         <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
         <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>12</v>
@@ -1041,7 +1056,7 @@
         <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J3" t="s">
         <v>23</v>
@@ -1052,39 +1067,39 @@
         <v>24</v>
       </c>
       <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
         <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
         <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -1099,24 +1114,24 @@
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1125,30 +1140,30 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
@@ -1163,13 +1178,13 @@
         <v>14</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H7" t="s">
         <v>41</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
         <v>42</v>
@@ -1195,13 +1210,13 @@
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
         <v>46</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J8" t="s">
         <v>47</v>
@@ -1212,7 +1227,7 @@
         <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -1221,30 +1236,30 @@
         <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
         <v>14</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
@@ -1253,30 +1268,30 @@
         <v>12</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
         <v>14</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
@@ -1291,13 +1306,13 @@
         <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H11" t="s">
         <v>59</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J11" t="s">
         <v>60</v>
@@ -1323,13 +1338,13 @@
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H12" t="s">
         <v>64</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" t="s">
         <v>65</v>
@@ -1340,7 +1355,7 @@
         <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
         <v>12</v>
@@ -1349,30 +1364,30 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H13" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
         <v>12</v>
@@ -1381,30 +1396,30 @@
         <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -1413,30 +1428,30 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -1451,13 +1466,13 @@
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H16" t="s">
         <v>81</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J16" t="s">
         <v>82</v>
@@ -1468,7 +1483,7 @@
         <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
         <v>12</v>
@@ -1477,30 +1492,30 @@
         <v>12</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F17" t="s">
         <v>14</v>
       </c>
       <c r="G17" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C18" t="s">
         <v>12</v>
@@ -1509,30 +1524,30 @@
         <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F18" t="s">
         <v>14</v>
       </c>
       <c r="G18" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -1541,30 +1556,30 @@
         <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F19" t="s">
         <v>14</v>
       </c>
       <c r="G19" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -1573,30 +1588,30 @@
         <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F20" t="s">
         <v>14</v>
       </c>
       <c r="G20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
@@ -1605,30 +1620,30 @@
         <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F21" t="s">
         <v>14</v>
       </c>
       <c r="G21" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
@@ -1637,30 +1652,30 @@
         <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F22" t="s">
         <v>14</v>
       </c>
       <c r="G22" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B23" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -1669,30 +1684,30 @@
         <v>12</v>
       </c>
       <c r="E23" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F23" t="s">
         <v>14</v>
       </c>
       <c r="G23" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H23" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="C24" t="s">
         <v>12</v>
@@ -1707,13 +1722,13 @@
         <v>14</v>
       </c>
       <c r="G24" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H24" t="s">
         <v>114</v>
       </c>
       <c r="I24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J24" t="s">
         <v>115</v>
@@ -1724,7 +1739,7 @@
         <v>116</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
         <v>12</v>
@@ -1733,30 +1748,30 @@
         <v>12</v>
       </c>
       <c r="E25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F25" t="s">
         <v>14</v>
       </c>
       <c r="G25" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
         <v>12</v>
@@ -1765,30 +1780,30 @@
         <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
         <v>12</v>
@@ -1797,30 +1812,30 @@
         <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B28" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
         <v>12</v>
@@ -1829,30 +1844,30 @@
         <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
         <v>12</v>
@@ -1861,30 +1876,30 @@
         <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="H29" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -1893,30 +1908,30 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H30" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J30" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C31" t="s">
         <v>12</v>
@@ -1925,30 +1940,30 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C32" t="s">
         <v>12</v>
@@ -1957,30 +1972,30 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H32" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J32" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C33" t="s">
         <v>12</v>
@@ -1989,30 +2004,30 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
       </c>
       <c r="G33" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C34" t="s">
         <v>12</v>
@@ -2021,30 +2036,30 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J34" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C35" t="s">
         <v>12</v>
@@ -2053,19 +2068,19 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
       </c>
       <c r="G35" t="s">
-        <v>158</v>
+        <v>21</v>
       </c>
       <c r="H35" t="s">
         <v>159</v>
       </c>
       <c r="I35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J35" t="s">
         <v>160</v>
@@ -2076,7 +2091,7 @@
         <v>161</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C36" t="s">
         <v>12</v>
@@ -2091,24 +2106,24 @@
         <v>14</v>
       </c>
       <c r="G36" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H36" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J36" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
@@ -2117,30 +2132,30 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
       </c>
       <c r="G37" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H37" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I37" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C38" t="s">
         <v>12</v>
@@ -2149,54 +2164,86 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
       </c>
       <c r="G38" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H38" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J38" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C39" t="s">
-        <v>174</v>
+        <v>12</v>
       </c>
       <c r="D39" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" t="s">
         <v>175</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>163</v>
+      </c>
+      <c r="H39" t="s">
         <v>176</v>
       </c>
-      <c r="F39" t="s">
+      <c r="I39" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" t="s">
         <v>177</v>
       </c>
-      <c r="G39" t="s">
-        <v>12</v>
-      </c>
-      <c r="H39" t="s">
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>178</v>
       </c>
-      <c r="I39" t="s">
-        <v>12</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="B40" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" t="s">
         <v>179</v>
+      </c>
+      <c r="D40" t="s">
+        <v>180</v>
+      </c>
+      <c r="E40" t="s">
+        <v>181</v>
+      </c>
+      <c r="F40" t="s">
+        <v>182</v>
+      </c>
+      <c r="G40" t="s">
+        <v>12</v>
+      </c>
+      <c r="H40" t="s">
+        <v>183</v>
+      </c>
+      <c r="I40" t="s">
+        <v>12</v>
+      </c>
+      <c r="J40" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
